--- a/EKG_Kalite_Yönetim_Sistemi/98_Uygulama_Kayıtları/04_Parça ve Proses Kontrolü/EKG-KLT-PLN-07_kontrol_plani__cfrl1_eski_kolon_duzeni.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/98_Uygulama_Kayıtları/04_Parça ve Proses Kontrolü/EKG-KLT-PLN-07_kontrol_plani__cfrl1_eski_kolon_duzeni.xlsx
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">04.05.2026</t>
+          <t xml:space="preserve">04.06.2026</t>
         </is>
       </c>
       <c r="M2" s="5"/>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">19.10.2026</t>
+          <t xml:space="preserve">10.09.2026</t>
         </is>
       </c>
       <c r="M4" s="4"/>
@@ -3526,7 +3526,8 @@
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="0" differentOddEven="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-PLN-07&amp;C&amp;"Arial,Regular"&amp;11Kontrol Planı - CFRL1 Eski Kolon Düzeni</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.06.2026 | Revizyon: 10.09.2026
+Revizyon nedeni: Kaynak kontrol planına, ürün bazlı teknik doğrulama ve onay gereğini açıklayan not eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
